--- a/Gant chart.xlsx
+++ b/Gant chart.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Finley\Desktop\BA diss\Bachelors-Dissertation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F24105C9-6F68-4658-BA14-06AD33D36851}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{927E48F6-053F-42DE-9E89-C2B7FC366F37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5AAA8AE7-F311-4EF6-A229-906B618A3298}"/>
   </bookViews>
@@ -36,27 +36,51 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
-  <si>
-    <t>Paper review</t>
-  </si>
-  <si>
-    <t>Construction of a PoC</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>Minimal work weeks</t>
   </si>
   <si>
-    <t>Extension sections</t>
-  </si>
-  <si>
-    <t>Report writing</t>
-  </si>
-  <si>
     <t>Normal weeks</t>
   </si>
   <si>
     <t>Reduced work weeks</t>
+  </si>
+  <si>
+    <t>Construction of a basic PoC</t>
+  </si>
+  <si>
+    <t>literature, technology and data survey</t>
+  </si>
+  <si>
+    <t>Development of obfuscation techniques</t>
+  </si>
+  <si>
+    <t>Development of a code artifact</t>
+  </si>
+  <si>
+    <t>Report updates</t>
+  </si>
+  <si>
+    <t>Report drafting</t>
+  </si>
+  <si>
+    <t>Report finalising</t>
+  </si>
+  <si>
+    <t>Deadlines</t>
+  </si>
+  <si>
+    <t>Exam period</t>
+  </si>
+  <si>
+    <t>Literature survey</t>
+  </si>
+  <si>
+    <t>Demonstration</t>
+  </si>
+  <si>
+    <t>Dissertation</t>
   </si>
 </sst>
 </file>
@@ -116,12 +140,68 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="5">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFFF0000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFFF0000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFF0000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFF0000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFFFC000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFFFC000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFC000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFC000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFFFC000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFFFC000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFC000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFFFC000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFC000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFC000"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -131,7 +211,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" textRotation="180"/>
@@ -139,6 +219,25 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="3"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="3" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" textRotation="180"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" textRotation="180"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" textRotation="180"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" textRotation="180"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Bad" xfId="2" builtinId="27"/>
@@ -476,11 +575,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69B82103-BC86-46F7-9BB6-F5EA3C18CD29}">
-  <dimension ref="A1:AA15"/>
+  <dimension ref="A1:AA17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="25.7109375" customWidth="1"/>
-    <col min="2" max="27" width="3.7109375" customWidth="1"/>
+    <col min="1" max="1" width="35.7109375" customWidth="1"/>
+    <col min="2" max="26" width="3.7109375" customWidth="1"/>
+    <col min="27" max="27" width="12.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -559,83 +659,183 @@
       <c r="Z1" s="1">
         <v>46139</v>
       </c>
-      <c r="AA1" s="1">
-        <v>46146</v>
-      </c>
+      <c r="AA1" s="1"/>
     </row>
     <row r="2" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B2" s="4"/>
       <c r="C2" s="4"/>
       <c r="D2" s="4"/>
+      <c r="E2" s="5"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="7"/>
+      <c r="P2" s="5"/>
+      <c r="Z2" s="5"/>
     </row>
     <row r="3" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="4"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2"/>
+      <c r="E3" s="5"/>
+      <c r="K3" s="7"/>
+      <c r="L3" s="7"/>
+      <c r="P3" s="5"/>
+      <c r="Z3" s="5"/>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="J4" s="4"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2"/>
-      <c r="N4" s="4"/>
-      <c r="O4" s="4"/>
-      <c r="P4" s="4"/>
-      <c r="Q4" s="4"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="2"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="7"/>
+      <c r="P4" s="5"/>
+      <c r="Z4" s="5"/>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="J5" s="4"/>
-      <c r="K5" s="2"/>
-      <c r="R5" s="4"/>
-      <c r="S5" s="4"/>
-      <c r="T5" s="4"/>
-      <c r="U5" s="4"/>
-      <c r="V5" s="4"/>
-      <c r="W5" s="4"/>
-      <c r="X5" s="2"/>
-      <c r="Y5" s="2"/>
-      <c r="Z5" s="3"/>
-      <c r="AA5" s="3"/>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
         <v>5</v>
       </c>
-      <c r="B13" s="4"/>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="E5" s="5"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="8"/>
+      <c r="L5" s="8"/>
+      <c r="M5" s="4"/>
+      <c r="P5" s="5"/>
+      <c r="Z5" s="5"/>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>6</v>
       </c>
-      <c r="B14" s="2"/>
+      <c r="E6" s="5"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="7"/>
+      <c r="N6" s="4"/>
+      <c r="O6" s="4"/>
+      <c r="P6" s="6"/>
+      <c r="Q6" s="4"/>
+      <c r="Z6" s="5"/>
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="E7" s="5"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="7"/>
+      <c r="P7" s="5"/>
+      <c r="Z7" s="5"/>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+      <c r="D8" s="4"/>
+      <c r="E8" s="5"/>
+      <c r="I8" s="4"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="4"/>
+      <c r="P8" s="5"/>
+      <c r="Q8" s="4"/>
+      <c r="Z8" s="5"/>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="5"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="7"/>
+      <c r="P9" s="5"/>
+      <c r="R9" s="4"/>
+      <c r="S9" s="4"/>
+      <c r="T9" s="4"/>
+      <c r="U9" s="4"/>
+      <c r="Z9" s="5"/>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="5"/>
+      <c r="K10" s="7"/>
+      <c r="L10" s="7"/>
+      <c r="P10" s="5"/>
+      <c r="V10" s="4"/>
+      <c r="W10" s="4"/>
+      <c r="X10" s="2"/>
+      <c r="Y10" s="2"/>
+      <c r="Z10" s="5"/>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="E11" s="5"/>
+      <c r="K11" s="7"/>
+      <c r="L11" s="7"/>
+      <c r="P11" s="5"/>
+      <c r="Z11" s="5"/>
+    </row>
+    <row r="12" spans="1:27" ht="77.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="10"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12" s="10"/>
+      <c r="G12" s="10"/>
+      <c r="H12" s="10"/>
+      <c r="I12" s="10"/>
+      <c r="J12" s="10"/>
+      <c r="K12" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="L12" s="13"/>
+      <c r="M12" s="10"/>
+      <c r="N12" s="10"/>
+      <c r="O12" s="10"/>
+      <c r="P12" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="Q12" s="10"/>
+      <c r="R12" s="10"/>
+      <c r="S12" s="10"/>
+      <c r="T12" s="10"/>
+      <c r="U12" s="10"/>
+      <c r="V12" s="10"/>
+      <c r="W12" s="10"/>
+      <c r="X12" s="10"/>
+      <c r="Y12" s="10"/>
+      <c r="Z12" s="11" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="15" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>1</v>
+      </c>
+      <c r="B15" s="4"/>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>2</v>
       </c>
-      <c r="B15" s="3"/>
+      <c r="B16" s="2"/>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>0</v>
+      </c>
+      <c r="B17" s="3"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="K12:L12"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>